--- a/India Meta Data.xlsx
+++ b/India Meta Data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DaolIM\Documents\Sharkky\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b8dbb841752bcc6d/Documents/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF6C5F7-4C93-4324-B25E-8FF7CA0F5BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BDF6C5F7-4C93-4324-B25E-8FF7CA0F5BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ACDA62E-A8A5-4CD2-AFD5-1E06C403F7B0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F3B8D9AC-425E-4138-9BCF-F736EB07B0E0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F3B8D9AC-425E-4138-9BCF-F736EB07B0E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -446,6 +447,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68ABE697-A6A7-4B64-9FE3-FF2A2BF8C2BE}">
   <dimension ref="A1:Z137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -11347,4 +11352,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852B0020-B77C-4B3E-A709-15FA51BF0F1E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>